--- a/main/ig/StructureDefinition-pdsm-simplified-publish.xlsx
+++ b/main/ig/StructureDefinition-pdsm-simplified-publish.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2527" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2527" uniqueCount="520">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-31T16:33:35+00:00</t>
+    <t>2025-04-24T12:56:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -395,17 +395,10 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>DocumentReference.meta.versionId</t>
   </si>
   <si>
@@ -507,12 +500,6 @@
     <t>Meta.security</t>
   </si>
   <si>
-    <t>CV</t>
-  </si>
-  <si>
-    <t>CE/CNE/CWE subset one of the sets of component 1-3 or 4-6</t>
-  </si>
-  <si>
     <t>DocumentReference.meta.tag</t>
   </si>
   <si>
@@ -627,6 +614,9 @@
   </si>
   <si>
     <t>DomainResource.contained</t>
+  </si>
+  <si>
+    <t>N/A</t>
   </si>
   <si>
     <t>DocumentReference.extension</t>
@@ -1980,15 +1970,15 @@
   <dimension ref="A1:AQ64"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="50.828125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="50.828125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="43.578125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="43.578125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1999,29 +1989,29 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="35.69140625" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="120.0625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="44.0703125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="30.6015625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="102.93359375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="37.78125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="52.0078125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="44.5859375" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="84.2265625" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="162.44921875" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="72.20703125" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="139.26953125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2739,11 +2729,11 @@
         <v>82</v>
       </c>
       <c r="AI6" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ6" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="AJ6" t="s" s="2">
-        <v>123</v>
-      </c>
       <c r="AK6" t="s" s="2">
         <v>80</v>
       </c>
@@ -2751,7 +2741,7 @@
         <v>80</v>
       </c>
       <c r="AM6" t="s" s="2">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="AN6" t="s" s="2">
         <v>80</v>
@@ -2768,10 +2758,10 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -2797,13 +2787,13 @@
         <v>95</v>
       </c>
       <c r="L7" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="M7" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="N7" t="s" s="2">
         <v>126</v>
-      </c>
-      <c r="M7" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>128</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2853,7 +2843,7 @@
         <v>80</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>81</v>
@@ -2862,7 +2852,7 @@
         <v>93</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>122</v>
+        <v>80</v>
       </c>
       <c r="AJ7" t="s" s="2">
         <v>105</v>
@@ -2874,7 +2864,7 @@
         <v>80</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="AN7" t="s" s="2">
         <v>80</v>
@@ -2891,10 +2881,10 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -2917,16 +2907,16 @@
         <v>94</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="L8" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="M8" t="s" s="2">
         <v>131</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>134</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2976,7 +2966,7 @@
         <v>80</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>81</v>
@@ -2985,7 +2975,7 @@
         <v>93</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>122</v>
+        <v>80</v>
       </c>
       <c r="AJ8" t="s" s="2">
         <v>105</v>
@@ -2997,7 +2987,7 @@
         <v>80</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="AN8" t="s" s="2">
         <v>80</v>
@@ -3014,10 +3004,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -3040,16 +3030,16 @@
         <v>94</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="M9" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>140</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -3099,7 +3089,7 @@
         <v>80</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>81</v>
@@ -3108,7 +3098,7 @@
         <v>93</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>122</v>
+        <v>80</v>
       </c>
       <c r="AJ9" t="s" s="2">
         <v>105</v>
@@ -3120,7 +3110,7 @@
         <v>80</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="AN9" t="s" s="2">
         <v>80</v>
@@ -3137,10 +3127,10 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -3163,16 +3153,16 @@
         <v>94</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="L10" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="L10" t="s" s="2">
+      <c r="N10" t="s" s="2">
         <v>144</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>146</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -3222,7 +3212,7 @@
         <v>80</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>81</v>
@@ -3231,7 +3221,7 @@
         <v>82</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>122</v>
+        <v>80</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>105</v>
@@ -3243,7 +3233,7 @@
         <v>80</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>80</v>
@@ -3260,10 +3250,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3286,16 +3276,16 @@
         <v>94</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="L11" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="M11" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="L11" t="s" s="2">
+      <c r="N11" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -3321,31 +3311,31 @@
         <v>80</v>
       </c>
       <c r="X11" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="Y11" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="Z11" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="Y11" t="s" s="2">
+      <c r="AA11" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB11" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC11" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD11" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE11" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF11" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="Z11" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="AA11" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB11" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC11" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD11" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE11" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF11" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>81</v>
@@ -3354,7 +3344,7 @@
         <v>82</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>122</v>
+        <v>80</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>105</v>
@@ -3366,7 +3356,7 @@
         <v>80</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>157</v>
+        <v>80</v>
       </c>
       <c r="AN11" t="s" s="2">
         <v>80</v>
@@ -3375,7 +3365,7 @@
         <v>80</v>
       </c>
       <c r="AP11" t="s" s="2">
-        <v>158</v>
+        <v>80</v>
       </c>
       <c r="AQ11" t="s" s="2">
         <v>80</v>
@@ -3383,10 +3373,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3409,16 +3399,16 @@
         <v>94</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3444,13 +3434,13 @@
         <v>80</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>80</v>
@@ -3468,7 +3458,7 @@
         <v>80</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>81</v>
@@ -3477,7 +3467,7 @@
         <v>82</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>122</v>
+        <v>80</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>105</v>
@@ -3489,7 +3479,7 @@
         <v>80</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>157</v>
+        <v>80</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>80</v>
@@ -3498,7 +3488,7 @@
         <v>80</v>
       </c>
       <c r="AP12" t="s" s="2">
-        <v>158</v>
+        <v>80</v>
       </c>
       <c r="AQ12" t="s" s="2">
         <v>80</v>
@@ -3506,10 +3496,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3532,16 +3522,16 @@
         <v>94</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3591,7 +3581,7 @@
         <v>80</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>81</v>
@@ -3629,10 +3619,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3655,16 +3645,16 @@
         <v>80</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3690,13 +3680,13 @@
         <v>80</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>80</v>
@@ -3714,7 +3704,7 @@
         <v>80</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>81</v>
@@ -3752,14 +3742,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3778,16 +3768,16 @@
         <v>80</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3837,7 +3827,7 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>81</v>
@@ -3858,7 +3848,7 @@
         <v>80</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>80</v>
@@ -3875,14 +3865,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3901,16 +3891,16 @@
         <v>80</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3960,7 +3950,7 @@
         <v>80</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>81</v>
@@ -3981,7 +3971,7 @@
         <v>80</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>124</v>
+        <v>192</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>80</v>
@@ -3998,10 +3988,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4030,7 +4020,7 @@
         <v>115</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="N17" t="s" s="2">
         <v>117</v>
@@ -4083,7 +4073,7 @@
         <v>80</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4095,7 +4085,7 @@
         <v>80</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>80</v>
@@ -4104,7 +4094,7 @@
         <v>80</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>124</v>
+        <v>192</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>80</v>
@@ -4121,10 +4111,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4150,10 +4140,10 @@
         <v>114</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4204,7 +4194,7 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4216,7 +4206,7 @@
         <v>80</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>80</v>
@@ -4242,10 +4232,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4268,19 +4258,19 @@
         <v>94</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="N19" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>80</v>
@@ -4329,7 +4319,7 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4344,33 +4334,33 @@
         <v>105</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="AM19" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="AN19" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="AL19" t="s" s="2">
+      <c r="AO19" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="AM19" t="s" s="2">
+      <c r="AP19" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="AN19" t="s" s="2">
+      <c r="AQ19" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="AO19" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="AP19" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="AQ19" t="s" s="2">
-        <v>215</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4393,13 +4383,13 @@
         <v>94</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4450,7 +4440,7 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4465,33 +4455,33 @@
         <v>105</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AQ20" t="s" s="2">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4514,16 +4504,16 @@
         <v>94</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4534,29 +4524,29 @@
         <v>80</v>
       </c>
       <c r="S21" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="T21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X21" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="Z21" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="T21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X21" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="Y21" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="Z21" t="s" s="2">
-        <v>229</v>
-      </c>
       <c r="AA21" t="s" s="2">
         <v>80</v>
       </c>
@@ -4573,7 +4563,7 @@
         <v>80</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>93</v>
@@ -4588,33 +4578,33 @@
         <v>105</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM21" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AN21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO21" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AP21" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="AL21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM21" t="s" s="2">
+      <c r="AQ21" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="AP21" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="AQ21" t="s" s="2">
-        <v>234</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4637,16 +4627,16 @@
         <v>94</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4672,13 +4662,13 @@
         <v>80</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>80</v>
@@ -4696,7 +4686,7 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4714,19 +4704,19 @@
         <v>80</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="AQ22" t="s" s="2">
         <v>80</v>
@@ -4734,10 +4724,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4760,16 +4750,16 @@
         <v>94</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="N23" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="L23" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4795,11 +4785,11 @@
         <v>80</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="Y23" s="2"/>
       <c r="Z23" t="s" s="2">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>80</v>
@@ -4817,7 +4807,7 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4829,40 +4819,40 @@
         <v>80</v>
       </c>
       <c r="AJ23" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AK23" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="AK23" t="s" s="2">
+      <c r="AN23" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="AL23" t="s" s="2">
+      <c r="AO23" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AP23" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="AN23" t="s" s="2">
+      <c r="AQ23" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="AP23" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="AQ23" t="s" s="2">
-        <v>257</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4881,16 +4871,16 @@
         <v>94</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4916,11 +4906,11 @@
         <v>80</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>80</v>
@@ -4938,7 +4928,7 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -4950,36 +4940,36 @@
         <v>80</v>
       </c>
       <c r="AJ24" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="AK24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AN24" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="AK24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL24" t="s" s="2">
+      <c r="AO24" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AP24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ24" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="AP24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ24" t="s" s="2">
-        <v>268</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5002,13 +4992,13 @@
         <v>94</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -5059,7 +5049,7 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -5074,37 +5064,37 @@
         <v>105</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AN25" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="AL25" t="s" s="2">
+      <c r="AO25" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AP25" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="AN25" t="s" s="2">
+      <c r="AQ25" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="AP25" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="AQ25" t="s" s="2">
-        <v>279</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -5123,16 +5113,16 @@
         <v>94</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5182,7 +5172,7 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5197,19 +5187,19 @@
         <v>105</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AN26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO26" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>80</v>
@@ -5220,10 +5210,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5246,16 +5236,16 @@
         <v>94</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="N27" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="L27" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5305,7 +5295,7 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5320,33 +5310,33 @@
         <v>105</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="AL27" t="s" s="2">
+      <c r="AO27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP27" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="AM27" t="s" s="2">
+      <c r="AQ27" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP27" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="AQ27" t="s" s="2">
-        <v>299</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5369,16 +5359,16 @@
         <v>80</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="N28" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="L28" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5428,7 +5418,7 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5443,33 +5433,33 @@
         <v>105</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="AL28" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AN28" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AO28" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="AM28" t="s" s="2">
+      <c r="AP28" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="AN28" t="s" s="2">
+      <c r="AQ28" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="AP28" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="AQ28" t="s" s="2">
-        <v>310</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5492,16 +5482,16 @@
         <v>80</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="N29" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="L29" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5551,7 +5541,7 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5566,13 +5556,13 @@
         <v>105</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>80</v>
@@ -5589,10 +5579,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5615,16 +5605,16 @@
         <v>94</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="N30" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="L30" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5674,7 +5664,7 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5692,10 +5682,10 @@
         <v>80</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>80</v>
@@ -5707,15 +5697,15 @@
         <v>80</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>325</v>
+        <v>322</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5833,10 +5823,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5930,7 +5920,7 @@
         <v>80</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>80</v>
@@ -5956,14 +5946,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5985,16 +5975,16 @@
         <v>114</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>117</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>80</v>
@@ -6043,7 +6033,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6055,7 +6045,7 @@
         <v>80</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>80</v>
@@ -6064,7 +6054,7 @@
         <v>80</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>124</v>
+        <v>192</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>80</v>
@@ -6081,10 +6071,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6107,16 +6097,16 @@
         <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6142,13 +6132,13 @@
         <v>80</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>80</v>
@@ -6166,7 +6156,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>93</v>
@@ -6184,10 +6174,10 @@
         <v>80</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>80</v>
@@ -6199,15 +6189,15 @@
         <v>80</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6230,13 +6220,13 @@
         <v>94</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6287,7 +6277,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>93</v>
@@ -6305,10 +6295,10 @@
         <v>80</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>80</v>
@@ -6320,15 +6310,15 @@
         <v>80</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6354,16 +6344,16 @@
         <v>107</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="O36" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>80</v>
@@ -6412,7 +6402,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6433,7 +6423,7 @@
         <v>80</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>80</v>
@@ -6442,18 +6432,18 @@
         <v>80</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6476,19 +6466,19 @@
         <v>94</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="O37" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>80</v>
@@ -6513,14 +6503,14 @@
         <v>80</v>
       </c>
       <c r="X37" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="Z37" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="Y37" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="Z37" t="s" s="2">
-        <v>155</v>
-      </c>
       <c r="AA37" t="s" s="2">
         <v>80</v>
       </c>
@@ -6537,7 +6527,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6549,36 +6539,36 @@
         <v>80</v>
       </c>
       <c r="AJ37" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="AK37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL37" t="s" s="2">
+      <c r="AO37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP37" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="AM37" t="s" s="2">
+      <c r="AQ37" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP37" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="AQ37" t="s" s="2">
-        <v>368</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6601,13 +6591,13 @@
         <v>94</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6658,7 +6648,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>93</v>
@@ -6676,10 +6666,10 @@
         <v>80</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>80</v>
@@ -6696,10 +6686,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6817,10 +6807,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6914,7 +6904,7 @@
         <v>80</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>80</v>
@@ -6940,14 +6930,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6969,16 +6959,16 @@
         <v>114</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="N41" t="s" s="2">
         <v>117</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>80</v>
@@ -7027,7 +7017,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7039,7 +7029,7 @@
         <v>80</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>80</v>
@@ -7048,7 +7038,7 @@
         <v>80</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>124</v>
+        <v>192</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>80</v>
@@ -7065,10 +7055,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7091,13 +7081,13 @@
         <v>94</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7148,7 +7138,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>93</v>
@@ -7166,30 +7156,30 @@
         <v>80</v>
       </c>
       <c r="AL42" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AN42" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AO42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP42" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AQ42" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP42" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="AQ42" t="s" s="2">
-        <v>384</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7307,10 +7297,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7404,7 +7394,7 @@
         <v>80</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>80</v>
@@ -7430,10 +7420,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7456,17 +7446,17 @@
         <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>80</v>
@@ -7479,43 +7469,43 @@
         <v>80</v>
       </c>
       <c r="T45" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF45" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="U45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X45" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="Y45" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="Z45" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="AA45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7536,7 +7526,7 @@
         <v>80</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>80</v>
@@ -7545,7 +7535,7 @@
         <v>80</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>80</v>
@@ -7553,10 +7543,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7579,17 +7569,17 @@
         <v>94</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>80</v>
@@ -7602,7 +7592,7 @@
         <v>80</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="U46" t="s" s="2">
         <v>80</v>
@@ -7614,13 +7604,13 @@
         <v>80</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>80</v>
@@ -7638,7 +7628,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7659,7 +7649,7 @@
         <v>80</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>80</v>
@@ -7676,10 +7666,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7702,19 +7692,19 @@
         <v>80</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="N47" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="O47" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>80</v>
@@ -7763,7 +7753,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7784,7 +7774,7 @@
         <v>80</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>80</v>
@@ -7793,7 +7783,7 @@
         <v>80</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>80</v>
@@ -7801,10 +7791,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7827,19 +7817,19 @@
         <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="N48" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>80</v>
@@ -7852,7 +7842,7 @@
         <v>80</v>
       </c>
       <c r="T48" t="s" s="2">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="U48" t="s" s="2">
         <v>80</v>
@@ -7888,7 +7878,7 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7909,7 +7899,7 @@
         <v>80</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>80</v>
@@ -7918,7 +7908,7 @@
         <v>80</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>80</v>
@@ -7926,10 +7916,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7952,19 +7942,19 @@
         <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="N49" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>80</v>
@@ -8013,7 +8003,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8034,7 +8024,7 @@
         <v>80</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>80</v>
@@ -8051,10 +8041,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8077,19 +8067,19 @@
         <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="O50" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>80</v>
@@ -8138,7 +8128,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8159,7 +8149,7 @@
         <v>80</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>80</v>
@@ -8176,10 +8166,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8205,14 +8195,14 @@
         <v>107</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>80</v>
@@ -8225,7 +8215,7 @@
         <v>80</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="U51" t="s" s="2">
         <v>80</v>
@@ -8261,7 +8251,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8282,7 +8272,7 @@
         <v>80</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>80</v>
@@ -8299,10 +8289,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8325,17 +8315,17 @@
         <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>80</v>
@@ -8384,7 +8374,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8405,7 +8395,7 @@
         <v>80</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>80</v>
@@ -8422,10 +8412,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8448,16 +8438,16 @@
         <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8483,11 +8473,11 @@
         <v>80</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>80</v>
@@ -8505,7 +8495,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8517,36 +8507,36 @@
         <v>80</v>
       </c>
       <c r="AJ53" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="AO53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ53" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="AK53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ53" t="s" s="2">
-        <v>459</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8569,16 +8559,16 @@
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8628,7 +8618,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8649,7 +8639,7 @@
         <v>80</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>80</v>
@@ -8666,10 +8656,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8787,10 +8777,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8884,7 +8874,7 @@
         <v>80</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>80</v>
@@ -8910,14 +8900,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8939,16 +8929,16 @@
         <v>114</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>117</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>80</v>
@@ -8997,7 +8987,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9009,7 +8999,7 @@
         <v>80</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>80</v>
@@ -9018,7 +9008,7 @@
         <v>80</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>124</v>
+        <v>192</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>80</v>
@@ -9035,10 +9025,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9061,13 +9051,13 @@
         <v>80</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9118,7 +9108,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9133,19 +9123,19 @@
         <v>105</v>
       </c>
       <c r="AK58" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO58" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>475</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>80</v>
@@ -9156,10 +9146,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9182,16 +9172,16 @@
         <v>80</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9217,13 +9207,13 @@
         <v>80</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>80</v>
@@ -9241,7 +9231,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9253,36 +9243,36 @@
         <v>80</v>
       </c>
       <c r="AJ59" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ59" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="AK59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ59" t="s" s="2">
-        <v>485</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9305,13 +9295,13 @@
         <v>94</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9362,7 +9352,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9380,30 +9370,30 @@
         <v>80</v>
       </c>
       <c r="AL60" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AO60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ60" t="s" s="2">
         <v>490</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ60" t="s" s="2">
-        <v>493</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9426,13 +9416,13 @@
         <v>80</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9459,11 +9449,11 @@
         <v>80</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="Y61" s="2"/>
       <c r="Z61" t="s" s="2">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>80</v>
@@ -9481,7 +9471,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9493,36 +9483,36 @@
         <v>80</v>
       </c>
       <c r="AJ61" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="AN61" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="AK61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL61" t="s" s="2">
+      <c r="AO61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ61" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ61" t="s" s="2">
-        <v>502</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9545,19 +9535,19 @@
         <v>80</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="O62" t="s" s="2">
         <v>504</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>507</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>80</v>
@@ -9582,11 +9572,11 @@
         <v>80</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="Y62" s="2"/>
       <c r="Z62" t="s" s="2">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>80</v>
@@ -9604,7 +9594,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9616,19 +9606,19 @@
         <v>80</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>80</v>
@@ -9637,15 +9627,15 @@
         <v>80</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>509</v>
+        <v>506</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9668,13 +9658,13 @@
         <v>80</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9725,7 +9715,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9743,13 +9733,13 @@
         <v>80</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>80</v>
@@ -9758,15 +9748,15 @@
         <v>80</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>513</v>
+        <v>510</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9789,16 +9779,16 @@
         <v>80</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="N64" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9848,7 +9838,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9866,22 +9856,22 @@
         <v>80</v>
       </c>
       <c r="AL64" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ64" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ64" t="s" s="2">
-        <v>522</v>
       </c>
     </row>
   </sheetData>

--- a/main/ig/StructureDefinition-pdsm-simplified-publish.xlsx
+++ b/main/ig/StructureDefinition-pdsm-simplified-publish.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T12:56:51+00:00</t>
+    <t>2025-04-24T12:57:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -787,7 +787,7 @@
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 constr-bind-type:Les valeurs possibles pour cet élément doivent provenir d’une des terminologies de référence suivantes :
  TRE_A05-TypeDocComplementaireCISIS, OID : 1.2.250.1.213.1.1.4.12
- TRE_A04-TypeDocument-LOINC, OID : 2.16.840.1.113883.6.1
+ LOINC, OID : 2.16.840.1.113883.6.1
  TRE_A12-NomenclatureASTM, OID : ASTM
 Les valeurs possibles peuvent être restreintes en fonction du jeu de valeurs correspondant mis à disposition par le projet (exemple : JDV_J66-TypeCode-DMP).
 En l’absence de spécifications complémentaires, le jeu de valeurs JDV_J07-XdsTypeCode-CISIS peut être utilisé. {null}</t>

--- a/main/ig/StructureDefinition-pdsm-simplified-publish.xlsx
+++ b/main/ig/StructureDefinition-pdsm-simplified-publish.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T12:57:11+00:00</t>
+    <t>2025-04-24T13:09:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-simplified-publish.xlsx
+++ b/main/ig/StructureDefinition-pdsm-simplified-publish.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T13:09:23+00:00</t>
+    <t>2025-04-29T14:26:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-simplified-publish.xlsx
+++ b/main/ig/StructureDefinition-pdsm-simplified-publish.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T14:28:01+00:00</t>
+    <t>2026-03-04T14:06:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-simplified-publish.xlsx
+++ b/main/ig/StructureDefinition-pdsm-simplified-publish.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-04T14:06:01+00:00</t>
+    <t>2026-03-04T14:38:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-simplified-publish.xlsx
+++ b/main/ig/StructureDefinition-pdsm-simplified-publish.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-04T14:38:02+00:00</t>
+    <t>2026-03-04T16:46:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-simplified-publish.xlsx
+++ b/main/ig/StructureDefinition-pdsm-simplified-publish.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2527" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2527" uniqueCount="520">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-04T16:46:41+00:00</t>
+    <t>2026-05-06T07:19:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -561,7 +561,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -987,7 +987,7 @@
     <t>DocumentReference.custodian</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1087,7 +1087,7 @@
     <t>DocumentReference.relatesTo.target</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference)
+    <t xml:space="preserve">Reference(DocumentReference|4.0.1)
 </t>
   </si>
   <si>
@@ -1144,9 +1144,6 @@
   </si>
   <si>
     <t>Use of the Health Care Privacy/Security Classification (HCS) system of security-tag use is recommended.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
@@ -1482,7 +1479,7 @@
     <t>DocumentReference.context.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter|EpisodeOfCare)
+    <t xml:space="preserve">Reference(Encounter|4.0.1|EpisodeOfCare|4.0.1)
 </t>
   </si>
   <si>
@@ -1631,7 +1628,7 @@
     <t>DocumentReference.context.related</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -6512,7 +6509,7 @@
         <v>152</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>360</v>
+        <v>153</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>80</v>
@@ -6542,36 +6539,36 @@
         <v>80</v>
       </c>
       <c r="AJ37" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL37" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="AK37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL37" t="s" s="2">
+      <c r="AM37" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="AM37" t="s" s="2">
+      <c r="AN37" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="AN37" t="s" s="2">
+      <c r="AO37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP37" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="AO37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP37" t="s" s="2">
+      <c r="AQ37" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="AQ37" t="s" s="2">
-        <v>366</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6597,10 +6594,10 @@
         <v>316</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6651,7 +6648,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>93</v>
@@ -6669,10 +6666,10 @@
         <v>80</v>
       </c>
       <c r="AL38" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>80</v>
@@ -6689,10 +6686,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6810,10 +6807,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6933,10 +6930,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7058,10 +7055,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7084,13 +7081,13 @@
         <v>94</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7141,7 +7138,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>93</v>
@@ -7159,30 +7156,30 @@
         <v>80</v>
       </c>
       <c r="AL42" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="AM42" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="AN42" t="s" s="2">
+      <c r="AO42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP42" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="AO42" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP42" t="s" s="2">
+      <c r="AQ42" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="AQ42" t="s" s="2">
-        <v>382</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7300,10 +7297,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7423,10 +7420,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7452,14 +7449,14 @@
         <v>169</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>80</v>
@@ -7472,7 +7469,7 @@
         <v>80</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="U45" t="s" s="2">
         <v>80</v>
@@ -7487,28 +7484,28 @@
         <v>224</v>
       </c>
       <c r="Y45" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="Z45" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="Z45" t="s" s="2">
+      <c r="AA45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF45" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="AA45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7529,16 +7526,16 @@
         <v>80</v>
       </c>
       <c r="AM45" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AN45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP45" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP45" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>80</v>
@@ -7546,10 +7543,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7575,14 +7572,14 @@
         <v>169</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>80</v>
@@ -7595,7 +7592,7 @@
         <v>80</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="U46" t="s" s="2">
         <v>80</v>
@@ -7631,7 +7628,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7652,7 +7649,7 @@
         <v>80</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>80</v>
@@ -7669,10 +7666,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7695,19 +7692,19 @@
         <v>80</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="N47" t="s" s="2">
+      <c r="O47" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>80</v>
@@ -7756,7 +7753,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7777,16 +7774,16 @@
         <v>80</v>
       </c>
       <c r="AM47" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP47" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP47" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>80</v>
@@ -7794,10 +7791,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7820,19 +7817,19 @@
         <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="N48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>80</v>
@@ -7845,43 +7842,43 @@
         <v>80</v>
       </c>
       <c r="T48" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF48" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="U48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF48" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7902,16 +7899,16 @@
         <v>80</v>
       </c>
       <c r="AM48" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP48" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP48" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>80</v>
@@ -7919,10 +7916,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7945,19 +7942,19 @@
         <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="N49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>80</v>
@@ -8006,7 +8003,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8027,7 +8024,7 @@
         <v>80</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>80</v>
@@ -8044,10 +8041,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8070,19 +8067,19 @@
         <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="N50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>80</v>
@@ -8131,7 +8128,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8152,7 +8149,7 @@
         <v>80</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>80</v>
@@ -8169,10 +8166,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8198,14 +8195,14 @@
         <v>107</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>80</v>
@@ -8218,43 +8215,43 @@
         <v>80</v>
       </c>
       <c r="T51" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF51" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="U51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8275,7 +8272,7 @@
         <v>80</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>80</v>
@@ -8292,10 +8289,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8318,17 +8315,17 @@
         <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>80</v>
@@ -8377,7 +8374,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8398,7 +8395,7 @@
         <v>80</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>80</v>
@@ -8415,10 +8412,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8444,13 +8441,13 @@
         <v>147</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8480,7 +8477,7 @@
       </c>
       <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>80</v>
@@ -8498,7 +8495,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8510,36 +8507,36 @@
         <v>80</v>
       </c>
       <c r="AJ53" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL53" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="AK53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL53" t="s" s="2">
+      <c r="AM53" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AN53" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="AM53" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="AN53" t="s" s="2">
+      <c r="AO53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ53" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP53" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ53" t="s" s="2">
-        <v>457</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8565,13 +8562,13 @@
         <v>316</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8621,7 +8618,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8642,7 +8639,7 @@
         <v>80</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>80</v>
@@ -8659,10 +8656,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8780,10 +8777,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8903,10 +8900,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9028,10 +9025,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9054,13 +9051,13 @@
         <v>80</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="M58" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9111,7 +9108,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9126,19 +9123,19 @@
         <v>105</v>
       </c>
       <c r="AK58" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AL58" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="AL58" t="s" s="2">
+      <c r="AM58" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="AM58" t="s" s="2">
+      <c r="AN58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO58" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>80</v>
@@ -9149,10 +9146,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9178,13 +9175,13 @@
         <v>242</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>475</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>476</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>477</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9213,11 +9210,11 @@
         <v>159</v>
       </c>
       <c r="Y59" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="Z59" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="Z59" t="s" s="2">
-        <v>479</v>
-      </c>
       <c r="AA59" t="s" s="2">
         <v>80</v>
       </c>
@@ -9234,7 +9231,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9246,36 +9243,36 @@
         <v>80</v>
       </c>
       <c r="AJ59" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL59" t="s" s="2">
         <v>480</v>
       </c>
-      <c r="AK59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL59" t="s" s="2">
+      <c r="AM59" t="s" s="2">
         <v>481</v>
       </c>
-      <c r="AM59" t="s" s="2">
+      <c r="AN59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ59" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ59" t="s" s="2">
-        <v>483</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9298,13 +9295,13 @@
         <v>94</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>487</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9355,7 +9352,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9373,30 +9370,30 @@
         <v>80</v>
       </c>
       <c r="AL60" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AM60" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="AM60" t="s" s="2">
+      <c r="AN60" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="AN60" t="s" s="2">
+      <c r="AO60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ60" t="s" s="2">
         <v>490</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ60" t="s" s="2">
-        <v>491</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9422,10 +9419,10 @@
         <v>242</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>493</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>494</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9456,7 +9453,7 @@
       </c>
       <c r="Y61" s="2"/>
       <c r="Z61" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>80</v>
@@ -9474,7 +9471,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9486,36 +9483,36 @@
         <v>80</v>
       </c>
       <c r="AJ61" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL61" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="AK61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL61" t="s" s="2">
+      <c r="AM61" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="AM61" t="s" s="2">
+      <c r="AN61" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="AN61" t="s" s="2">
+      <c r="AO61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ61" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ61" t="s" s="2">
-        <v>500</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9541,16 +9538,16 @@
         <v>242</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>502</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>503</v>
       </c>
-      <c r="N62" t="s" s="2">
+      <c r="O62" t="s" s="2">
         <v>504</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>505</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>80</v>
@@ -9579,7 +9576,7 @@
       </c>
       <c r="Y62" s="2"/>
       <c r="Z62" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>80</v>
@@ -9597,7 +9594,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9609,19 +9606,19 @@
         <v>80</v>
       </c>
       <c r="AJ62" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL62" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="AK62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL62" t="s" s="2">
+      <c r="AM62" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="AM62" t="s" s="2">
-        <v>498</v>
-      </c>
       <c r="AN62" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>80</v>
@@ -9630,15 +9627,15 @@
         <v>80</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9664,10 +9661,10 @@
         <v>267</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9718,7 +9715,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9751,15 +9748,15 @@
         <v>80</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9782,16 +9779,16 @@
         <v>80</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="L64" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="M64" t="s" s="2">
         <v>514</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9841,7 +9838,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9859,22 +9856,22 @@
         <v>80</v>
       </c>
       <c r="AL64" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="AM64" t="s" s="2">
         <v>517</v>
       </c>
-      <c r="AM64" t="s" s="2">
+      <c r="AN64" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="AN64" t="s" s="2">
+      <c r="AO64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ64" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ64" t="s" s="2">
-        <v>520</v>
       </c>
     </row>
   </sheetData>

--- a/main/ig/StructureDefinition-pdsm-simplified-publish.xlsx
+++ b/main/ig/StructureDefinition-pdsm-simplified-publish.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:19:11+00:00</t>
+    <t>2026-05-27T14:14:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -953,11 +953,11 @@
     <t>DocumentReference.authenticator</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitionerrole|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitioner|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitionerrole|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization)
 </t>
   </si>
   <si>
-    <t>Cet attribut représente l’acteur validant le document et prenant la responsabilité du contenu médical de celui-ci. Il peut s’agir de l’auteur du document si celui-ci est une personne et s’il endosse la responsabilité du contenu médical de ses documents. Si l’auteur est un dispositif, cet attribut doit représenter la personne responsable de l’action effectuée par le dispositif.</t>
+    <t>Cet attribut représente l’acteur validant le document et prenant la responsabilité du contenu médical de celui-ci. Il peut s’agir de l’auteur du document si celui-ci est une personne et s’il endosse la responsabilité du contenu médical de ses documents.</t>
   </si>
   <si>
     <t>Which person or organization authenticates that this document is valid.</t>

--- a/main/ig/StructureDefinition-pdsm-simplified-publish.xlsx
+++ b/main/ig/StructureDefinition-pdsm-simplified-publish.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T14:14:06+00:00</t>
+    <t>2026-05-28T14:04:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>93</v>

--- a/main/ig/StructureDefinition-pdsm-simplified-publish.xlsx
+++ b/main/ig/StructureDefinition-pdsm-simplified-publish.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T14:04:20+00:00</t>
+    <t>2026-05-28T14:30:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -991,10 +991,10 @@
 </t>
   </si>
   <si>
-    <t>Organization which maintains the document</t>
-  </si>
-  <si>
-    <t>Identifies the organization or group who is responsible for ongoing maintenance of and access to the document.</t>
+    <t>Organisme responsable de la gestion du document. Dans le cadre XDS, il s'agit d'une information transmise dans le VIHF.</t>
+  </si>
+  <si>
+    <t>Correspond à l’organisation responsable de la conservation, de la maintenance et/ou de l’accès au document, et non nécessairement à l’auteur ou à l’hébergeur technique.</t>
   </si>
   <si>
     <t>Identifies the logical organization (software system, vendor, or department) to go to find the current version, where to report issues, etc. This is different from the physical location (URL, disk drive, or server) of the document, which is the technical location of the document, which host may be delegated to the management of some other organization.</t>
@@ -5467,7 +5467,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>93</v>

--- a/main/ig/StructureDefinition-pdsm-simplified-publish.xlsx
+++ b/main/ig/StructureDefinition-pdsm-simplified-publish.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T14:30:01+00:00</t>
+    <t>2026-06-03T13:49:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-simplified-publish.xlsx
+++ b/main/ig/StructureDefinition-pdsm-simplified-publish.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T13:49:29+00:00</t>
+    <t>2026-06-03T13:50:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-simplified-publish.xlsx
+++ b/main/ig/StructureDefinition-pdsm-simplified-publish.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T13:50:50+00:00</t>
+    <t>2026-06-30T13:26:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-simplified-publish.xlsx
+++ b/main/ig/StructureDefinition-pdsm-simplified-publish.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T13:26:19+00:00</t>
+    <t>2026-06-30T13:34:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-simplified-publish.xlsx
+++ b/main/ig/StructureDefinition-pdsm-simplified-publish.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2527" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2526" uniqueCount="520">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T13:34:41+00:00</t>
+    <t>2026-06-30T16:19:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1146,8 +1146,7 @@
     <t>Use of the Health Care Privacy/Security Classification (HCS) system of security-tag use is recommended.</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-constr-bind-securityLabel:Les codes pour cet élément doivent provenir du ValueSet spécifié par le standard. Lorsqu’aucun code ne correspond au concept recherché, un code provenant de la terminologie de référence TRE_A07-StatusVisibiliteDocument, OID : 1.2.250.1.213.1.1.4.13 peut être utilisé. {null}</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J08-XdsConfidentialityCode-CISIS/FHIR/JDV-J08-XdsConfidentialityCode-CISIS</t>
   </si>
   <si>
     <t>Composition.confidentiality, Composition.meta.security</t>
@@ -6505,11 +6504,9 @@
       <c r="X37" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="Y37" t="s" s="2">
-        <v>152</v>
-      </c>
+      <c r="Y37" s="2"/>
       <c r="Z37" t="s" s="2">
-        <v>153</v>
+        <v>360</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>80</v>
@@ -6539,7 +6536,7 @@
         <v>80</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>360</v>
+        <v>105</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>80</v>

--- a/main/ig/StructureDefinition-pdsm-simplified-publish.xlsx
+++ b/main/ig/StructureDefinition-pdsm-simplified-publish.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T16:19:40+00:00</t>
+    <t>2026-07-15T16:15:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profil utilisé dans le cadre du flux 9 d'ajout simplifié de document. Le flux et le profil sont inspirés d’IHE MHD, transaction ITI-105.
+    <t>Profil utilisé dans le cadre du flux 9 de publication simplifiée de document. Le flux et le profil sont inspirés d’IHE MHD, transaction ITI-105.
 Contrairement au profil PDSm_ComprehensiveDocumentReference, le document est directement inclus dans DocumentReference.attachment.data et non dans une ressource « Binary » externe.
 La publication simplifiée est une simple requête HTTP POST d'une ressource DocumentReference conforme à ce profil.</t>
   </si>

--- a/main/ig/StructureDefinition-pdsm-simplified-publish.xlsx
+++ b/main/ig/StructureDefinition-pdsm-simplified-publish.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2526" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2526" uniqueCount="523">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T16:15:50+00:00</t>
+    <t>2026-07-27T15:55:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1013,13 +1013,17 @@
 </t>
   </si>
   <si>
-    <t>Relationships to other documents</t>
-  </si>
-  <si>
-    <t>Relationships that this document has with other document references that already exist.</t>
+    <t>Relation avec le document remplacé</t>
+  </si>
+  <si>
+    <t>Renseigné lorsque le flux envoyé correspond au remplacement d’un document existant.</t>
   </si>
   <si>
     <t>This element is labeled as a modifier because documents that append to other documents are incomplete on their own.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+constr-sp-relatesTo-rempl:Renseigné lorsque le flux envoyé correspond au remplacement d’un document existant. {null}</t>
   </si>
   <si>
     <t>Composition.relatesTo</t>
@@ -1060,7 +1064,7 @@
     <t>DocumentReference.relatesTo.code</t>
   </si>
   <si>
-    <t>replaces | transforms | signs | appends</t>
+    <t>Représente le type d’association entre deux documents.</t>
   </si>
   <si>
     <t>The type of relationship that this document has with anther document.</t>
@@ -1073,6 +1077,10 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/document-relationship-type|4.0.1</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+constr-sp-bind-relatesToCode:Doit valoir « replaces » lorsque le flux envoyé correspond au remplacement d’un document existant. {null}</t>
   </si>
   <si>
     <t>Composition.relatesTo.code</t>
@@ -1091,10 +1099,14 @@
 </t>
   </si>
   <si>
-    <t>Target of the relationship</t>
+    <t>Représente l’identifiant du document remplacé.</t>
   </si>
   <si>
     <t>The target document of this relationship.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+constr-sp-bind-relatesToTarget:Référence contrainte au profil PDSm_SimplifiedPublish. {null}</t>
   </si>
   <si>
     <t>Composition.relatesTo.target</t>
@@ -5675,16 +5687,16 @@
         <v>80</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>105</v>
+        <v>320</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>80</v>
@@ -5696,15 +5708,15 @@
         <v>80</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5822,10 +5834,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5945,14 +5957,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5974,16 +5986,16 @@
         <v>114</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>117</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>80</v>
@@ -6032,7 +6044,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6070,10 +6082,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6099,13 +6111,13 @@
         <v>169</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6134,10 +6146,10 @@
         <v>224</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>80</v>
@@ -6155,7 +6167,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>93</v>
@@ -6167,16 +6179,16 @@
         <v>80</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>105</v>
+        <v>338</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>80</v>
@@ -6188,15 +6200,15 @@
         <v>80</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6219,13 +6231,13 @@
         <v>94</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6276,7 +6288,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>93</v>
@@ -6288,16 +6300,16 @@
         <v>80</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>105</v>
+        <v>346</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>80</v>
@@ -6309,15 +6321,15 @@
         <v>80</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6343,16 +6355,16 @@
         <v>107</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>80</v>
@@ -6401,7 +6413,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6422,7 +6434,7 @@
         <v>80</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>80</v>
@@ -6431,18 +6443,18 @@
         <v>80</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6468,16 +6480,16 @@
         <v>242</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>80</v>
@@ -6506,7 +6518,7 @@
       </c>
       <c r="Y37" s="2"/>
       <c r="Z37" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>80</v>
@@ -6524,7 +6536,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6542,30 +6554,30 @@
         <v>80</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6591,10 +6603,10 @@
         <v>316</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6645,7 +6657,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>93</v>
@@ -6663,10 +6675,10 @@
         <v>80</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>80</v>
@@ -6683,10 +6695,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6804,10 +6816,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6927,14 +6939,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6956,16 +6968,16 @@
         <v>114</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N41" t="s" s="2">
         <v>117</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>80</v>
@@ -7014,7 +7026,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7052,10 +7064,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7078,13 +7090,13 @@
         <v>94</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7135,7 +7147,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>93</v>
@@ -7153,30 +7165,30 @@
         <v>80</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7294,10 +7306,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7417,10 +7429,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7446,14 +7458,14 @@
         <v>169</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>80</v>
@@ -7466,7 +7478,7 @@
         <v>80</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="U45" t="s" s="2">
         <v>80</v>
@@ -7481,10 +7493,10 @@
         <v>224</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>80</v>
@@ -7502,7 +7514,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7523,7 +7535,7 @@
         <v>80</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>80</v>
@@ -7532,7 +7544,7 @@
         <v>80</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>80</v>
@@ -7540,10 +7552,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7569,14 +7581,14 @@
         <v>169</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>80</v>
@@ -7589,7 +7601,7 @@
         <v>80</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="U46" t="s" s="2">
         <v>80</v>
@@ -7625,7 +7637,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7646,7 +7658,7 @@
         <v>80</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>80</v>
@@ -7663,10 +7675,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7689,19 +7701,19 @@
         <v>80</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>80</v>
@@ -7750,7 +7762,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7771,7 +7783,7 @@
         <v>80</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>80</v>
@@ -7780,7 +7792,7 @@
         <v>80</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>80</v>
@@ -7788,10 +7800,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7814,19 +7826,19 @@
         <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>80</v>
@@ -7839,7 +7851,7 @@
         <v>80</v>
       </c>
       <c r="T48" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="U48" t="s" s="2">
         <v>80</v>
@@ -7875,7 +7887,7 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7896,7 +7908,7 @@
         <v>80</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>80</v>
@@ -7905,7 +7917,7 @@
         <v>80</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>80</v>
@@ -7913,10 +7925,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7939,19 +7951,19 @@
         <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>80</v>
@@ -8000,7 +8012,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8021,7 +8033,7 @@
         <v>80</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>80</v>
@@ -8038,10 +8050,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8064,19 +8076,19 @@
         <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>80</v>
@@ -8125,7 +8137,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8146,7 +8158,7 @@
         <v>80</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>80</v>
@@ -8163,10 +8175,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8192,14 +8204,14 @@
         <v>107</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>80</v>
@@ -8212,7 +8224,7 @@
         <v>80</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="U51" t="s" s="2">
         <v>80</v>
@@ -8248,7 +8260,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8269,7 +8281,7 @@
         <v>80</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>80</v>
@@ -8286,10 +8298,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8312,17 +8324,17 @@
         <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>80</v>
@@ -8371,7 +8383,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8392,7 +8404,7 @@
         <v>80</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>80</v>
@@ -8409,10 +8421,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8438,13 +8450,13 @@
         <v>147</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8474,7 +8486,7 @@
       </c>
       <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>80</v>
@@ -8492,7 +8504,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8504,19 +8516,19 @@
         <v>80</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>80</v>
@@ -8525,15 +8537,15 @@
         <v>80</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8559,13 +8571,13 @@
         <v>316</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8615,7 +8627,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8636,7 +8648,7 @@
         <v>80</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>80</v>
@@ -8653,10 +8665,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8774,10 +8786,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8897,14 +8909,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8926,16 +8938,16 @@
         <v>114</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>117</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>80</v>
@@ -8984,7 +8996,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9022,10 +9034,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9048,13 +9060,13 @@
         <v>80</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9105,7 +9117,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9120,19 +9132,19 @@
         <v>105</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>80</v>
@@ -9143,10 +9155,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9172,13 +9184,13 @@
         <v>242</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9207,10 +9219,10 @@
         <v>159</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>80</v>
@@ -9228,7 +9240,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9240,16 +9252,16 @@
         <v>80</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>80</v>
@@ -9261,15 +9273,15 @@
         <v>80</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9292,13 +9304,13 @@
         <v>94</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9349,7 +9361,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9367,13 +9379,13 @@
         <v>80</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>80</v>
@@ -9382,15 +9394,15 @@
         <v>80</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9416,10 +9428,10 @@
         <v>242</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9450,25 +9462,25 @@
       </c>
       <c r="Y61" s="2"/>
       <c r="Z61" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF61" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>491</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9480,19 +9492,19 @@
         <v>80</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>80</v>
@@ -9501,15 +9513,15 @@
         <v>80</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9535,16 +9547,16 @@
         <v>242</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>80</v>
@@ -9573,7 +9585,7 @@
       </c>
       <c r="Y62" s="2"/>
       <c r="Z62" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>80</v>
@@ -9591,7 +9603,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9603,19 +9615,19 @@
         <v>80</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>80</v>
@@ -9624,15 +9636,15 @@
         <v>80</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9658,10 +9670,10 @@
         <v>267</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9712,7 +9724,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9745,15 +9757,15 @@
         <v>80</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9776,16 +9788,16 @@
         <v>80</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9835,7 +9847,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9853,13 +9865,13 @@
         <v>80</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>80</v>
@@ -9868,7 +9880,7 @@
         <v>80</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>

--- a/main/ig/StructureDefinition-pdsm-simplified-publish.xlsx
+++ b/main/ig/StructureDefinition-pdsm-simplified-publish.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T15:55:54+00:00</t>
+    <t>2026-08-06T13:06:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-simplified-publish.xlsx
+++ b/main/ig/StructureDefinition-pdsm-simplified-publish.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:06:39+00:00</t>
+    <t>2026-08-06T14:18:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-simplified-publish.xlsx
+++ b/main/ig/StructureDefinition-pdsm-simplified-publish.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T14:18:59+00:00</t>
+    <t>2026-08-06T14:57:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
